--- a/artfynd/A 11351-2022 artfynd.xlsx
+++ b/artfynd/A 11351-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 11351-2022 artfynd.xlsx
+++ b/artfynd/A 11351-2022 artfynd.xlsx
@@ -675,43 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100015937</v>
+        <v>100016047</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>618974.9011704492</v>
+        <v>619016</v>
       </c>
       <c r="R2" t="n">
-        <v>6908872.783339369</v>
+        <v>6908731</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -752,19 +746,9 @@
           <t>2022-04-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-04-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,43 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100015898</v>
+        <v>100016267</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -836,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>618958.2781875312</v>
+        <v>618978</v>
       </c>
       <c r="R3" t="n">
-        <v>6908749.714755565</v>
+        <v>6908425</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -869,19 +847,9 @@
           <t>2022-04-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-04-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100015825</v>
+        <v>100015775</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -953,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618938.4013052222</v>
+        <v>618943</v>
       </c>
       <c r="R4" t="n">
-        <v>6908652.607028574</v>
+        <v>6908608</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -986,19 +949,9 @@
           <t>2022-04-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-04-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,15 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>100016001</v>
+        <v>100015825</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,10 +1018,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>619081.5940804497</v>
+        <v>618939</v>
       </c>
       <c r="R5" t="n">
-        <v>6908796.934424342</v>
+        <v>6908653</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1103,19 +1051,9 @@
           <t>2022-04-17</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-04-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,42 +1081,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>100016047</v>
+        <v>100015898</v>
       </c>
       <c r="B6" t="n">
-        <v>73680</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>306</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1186,10 +1120,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>619016.7635559073</v>
+        <v>618959</v>
       </c>
       <c r="R6" t="n">
-        <v>6908731.297732434</v>
+        <v>6908749</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1219,19 +1153,9 @@
           <t>2022-04-17</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-04-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,15 +1183,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>100015775</v>
+        <v>100015911</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1303,10 +1222,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618943.2285177469</v>
+        <v>618944</v>
       </c>
       <c r="R7" t="n">
-        <v>6908608.534303765</v>
+        <v>6908755</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1336,19 +1255,9 @@
           <t>2022-04-17</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-04-17</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,15 +1285,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>100015988</v>
+        <v>100015920</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>619038.3485566998</v>
+        <v>618964</v>
       </c>
       <c r="R8" t="n">
-        <v>6908819.616201789</v>
+        <v>6908810</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1453,19 +1357,9 @@
           <t>2022-04-17</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-04-17</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,15 +1387,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>100016074</v>
+        <v>100015937</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,10 +1426,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>618987.4043922224</v>
+        <v>618974</v>
       </c>
       <c r="R9" t="n">
-        <v>6908520.213941136</v>
+        <v>6908872</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1570,19 +1459,9 @@
           <t>2022-04-17</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-04-17</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,15 +1489,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>100016038</v>
+        <v>100015949</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1654,10 +1528,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>619077.582210796</v>
+        <v>618977</v>
       </c>
       <c r="R10" t="n">
-        <v>6908726.004378062</v>
+        <v>6908871</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1687,19 +1561,9 @@
           <t>2022-04-17</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-04-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,15 +1591,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>100015920</v>
+        <v>100015957</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,10 +1630,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>618963.5869412565</v>
+        <v>618963</v>
       </c>
       <c r="R11" t="n">
-        <v>6908810.444558854</v>
+        <v>6908817</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1804,19 +1663,9 @@
           <t>2022-04-17</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-04-17</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1844,42 +1693,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>100016267</v>
+        <v>100015977</v>
       </c>
       <c r="B12" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1887,10 +1732,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>618978.6575261204</v>
+        <v>618999</v>
       </c>
       <c r="R12" t="n">
-        <v>6908424.891379546</v>
+        <v>6908806</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1920,19 +1765,9 @@
           <t>2022-04-17</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-04-17</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1960,15 +1795,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>100015957</v>
+        <v>100015988</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2004,10 +1834,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>618963.7888497028</v>
+        <v>619038</v>
       </c>
       <c r="R13" t="n">
-        <v>6908817.902913093</v>
+        <v>6908820</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2037,19 +1867,9 @@
           <t>2022-04-17</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-04-17</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2077,15 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>100016022</v>
+        <v>100016001</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,10 +1936,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>619116.4689398624</v>
+        <v>619082</v>
       </c>
       <c r="R14" t="n">
-        <v>6908760.450268403</v>
+        <v>6908797</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2154,19 +1969,9 @@
           <t>2022-04-17</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-04-17</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2194,15 +1999,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>100015977</v>
+        <v>100016022</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2238,10 +2038,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>618998.7193862887</v>
+        <v>619116</v>
       </c>
       <c r="R15" t="n">
-        <v>6908806.102110915</v>
+        <v>6908760</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2271,19 +2071,9 @@
           <t>2022-04-17</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-04-17</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2314,12 +2104,7 @@
         <v>100016030</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2355,10 +2140,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>619042.5808222232</v>
+        <v>619043</v>
       </c>
       <c r="R16" t="n">
-        <v>6908726.625132693</v>
+        <v>6908727</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2388,19 +2173,9 @@
           <t>2022-04-17</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-04-17</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2428,15 +2203,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>100015911</v>
+        <v>100016038</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2472,10 +2242,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>618944.5555736783</v>
+        <v>619078</v>
       </c>
       <c r="R17" t="n">
-        <v>6908755.282424181</v>
+        <v>6908726</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2505,19 +2275,9 @@
           <t>2022-04-17</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-04-17</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2545,15 +2305,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>100015949</v>
+        <v>100016074</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,10 +2344,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>618976.7972973661</v>
+        <v>618987</v>
       </c>
       <c r="R18" t="n">
-        <v>6908871.919199955</v>
+        <v>6908520</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2622,19 +2377,9 @@
           <t>2022-04-17</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-04-17</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 11351-2022 artfynd.xlsx
+++ b/artfynd/A 11351-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100016047</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100016267</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100015775</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100015825</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1180,6 +1205,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100015898</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,6 +1312,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100015911</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,6 +1419,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100015920</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1486,6 +1526,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100015937</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1588,6 +1633,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100015949</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1690,6 +1740,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100015957</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1792,6 +1847,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100015977</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1894,6 +1954,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100015988</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1996,6 +2061,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100016001</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2098,6 +2168,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100016022</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2200,6 +2275,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100016030</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2302,6 +2382,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100016038</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2404,8 +2489,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100016074</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>